--- a/tame_output/ON/bt/strategyON_20241002.xlsx
+++ b/tame_output/ON/bt/strategyON_20241002.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.6%</t>
+          <t>420.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.3%</t>
+          <t>-615.1%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-65.5%</t>
+          <t>-65.4%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.8%</t>
+          <t>-205.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.6%</t>
+          <t>-96.4%</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>114.9%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>122.7%</t>
+          <t>122.8%</t>
         </is>
       </c>
     </row>
@@ -49736,16 +49736,16 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.360254451132779</v>
+        <v>-5.407580303646429</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.792331539118452</v>
+        <v>2.773401198112992</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8237158546486703</v>
+        <v>0.776390002135021</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.431019256674514</v>
+        <v>5.402623745166324</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.197146458979164</v>
+        <v>-5.244472311492814</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.853982403694832</v>
+        <v>2.835052062689372</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.9394979942886362</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.525291719681618</v>
+        <v>5.496896208173428</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.064338833481997</v>
+        <v>-5.111664685995647</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.916152490584827</v>
+        <v>2.897222149579367</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.9394979942886362</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.534338756372746</v>
+        <v>5.505943244864556</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.127046749956556</v>
+        <v>-5.174372602470205</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.891926788981126</v>
+        <v>2.872996447975666</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9241159303277278</v>
+        <v>0.8767900778140785</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.497571471474132</v>
+        <v>5.469175959965943</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.079038626112863</v>
+        <v>-5.126364478626512</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.874039455308955</v>
+        <v>2.855109114303495</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9241159303277278</v>
+        <v>0.8767900778140785</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.460480888264485</v>
+        <v>5.432085376756295</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.000212968929272</v>
+        <v>-5.047538821442922</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.909501971740342</v>
+        <v>2.890571630734882</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.002941587511318</v>
+        <v>0.9556157349976689</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.511708536132589</v>
+        <v>5.4833130246244</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.808278167675399</v>
+        <v>-4.855604020189048</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.981174984848928</v>
+        <v>2.962244643843468</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.002941587511318</v>
+        <v>0.9556157349976689</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.506607628739626</v>
+        <v>5.478212117231437</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.690104789657472</v>
+        <v>-4.737430642171121</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.023798245445194</v>
+        <v>3.004867904439734</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.121114965529245</v>
+        <v>1.073789113015596</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.572865564939478</v>
+        <v>5.544470053431288</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.57669010687474</v>
+        <v>-4.62401595938839</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.098252711421313</v>
+        <v>3.079322370415854</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.234529648311977</v>
+        <v>1.187203795798327</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.670002967472143</v>
+        <v>5.641607455963954</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.761930767118464</v>
+        <v>3.756775366761264</v>
       </c>
       <c r="C2104" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.537396383285288</v>
+        <v>-4.535542242145082</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.107530423868272</v>
+        <v>3.108272080324354</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.273823371901429</v>
+        <v>1.275677513041635</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.687139424636992</v>
+        <v>5.688251909321116</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241002.xlsx
+++ b/tame_output/ON/bt/strategyON_20241002.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>180.7%</t>
+          <t>184.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.7%</t>
+          <t>420.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.1%</t>
+          <t>-616.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-65.4%</t>
+          <t>-62.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-205.1%</t>
+          <t>-204.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.4%</t>
+          <t>-97.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>126.0%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>116.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>122.8%</t>
+          <t>125.4%</t>
         </is>
       </c>
     </row>
@@ -49250,19 +49250,19 @@
         <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.013119867577777</v>
+        <v>4.047942477975778</v>
       </c>
       <c r="D2074" t="n">
         <v>-5.425076287933173</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.84273292809076</v>
+        <v>1.877555538488761</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.350243986196018</v>
+        <v>4.385066596594019</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.023284378622827</v>
+        <v>4.058106989020827</v>
       </c>
       <c r="D2075" t="n">
         <v>-5.516458850498632</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.816344414109626</v>
+        <v>1.851167024507627</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.338469566409461</v>
+        <v>4.373292176807461</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.125412636447095</v>
+        <v>4.160235246845096</v>
       </c>
       <c r="D2076" t="n">
         <v>-5.504752132511626</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.923155359128697</v>
+        <v>1.957977969526697</v>
       </c>
       <c r="F2076" t="n">
         <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.447621855025933</v>
+        <v>4.482444465423933</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.1284449751785</v>
+        <v>4.1632675855765</v>
       </c>
       <c r="D2077" t="n">
         <v>-5.575664206253903</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.897822868363191</v>
+        <v>1.932645478761192</v>
       </c>
       <c r="F2077" t="n">
         <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.450654193757337</v>
+        <v>4.485476804155338</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341349808456558</v>
+        <v>4.376172418854559</v>
       </c>
       <c r="D2078" t="n">
         <v>-5.585980304420255</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.106601262374708</v>
+        <v>2.141423872772709</v>
       </c>
       <c r="F2078" t="n">
         <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.663559027035395</v>
+        <v>4.698381637433396</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.340528475368647</v>
+        <v>4.375351085766648</v>
       </c>
       <c r="D2079" t="n">
         <v>-5.585886336402882</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.105817516493747</v>
+        <v>2.140640126891748</v>
       </c>
       <c r="F2079" t="n">
         <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.662959610755876</v>
+        <v>4.697782221153877</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.334760461313001</v>
+        <v>4.369583071711002</v>
       </c>
       <c r="D2080" t="n">
         <v>-5.734252564059027</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.040703011375643</v>
+        <v>2.075525621773644</v>
       </c>
       <c r="F2080" t="n">
         <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.65719159670023</v>
+        <v>4.69201420709823</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.334760461313001</v>
+        <v>4.369583071711002</v>
       </c>
       <c r="D2081" t="n">
         <v>-5.733304140940988</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.041082380622858</v>
+        <v>2.075904991020859</v>
       </c>
       <c r="F2081" t="n">
         <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.65719159670023</v>
+        <v>4.69201420709823</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347488069294093</v>
+        <v>4.382310679692094</v>
       </c>
       <c r="D2082" t="n">
         <v>-5.83357395890001</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.013702061420342</v>
+        <v>2.048524671818342</v>
       </c>
       <c r="F2082" t="n">
         <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.669919204681322</v>
+        <v>4.704741815079323</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349434067718481</v>
+        <v>4.384256678116482</v>
       </c>
       <c r="D2083" t="n">
         <v>-5.827581712111198</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.018044958560254</v>
+        <v>2.052867568958255</v>
       </c>
       <c r="F2083" t="n">
         <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.67186520310571</v>
+        <v>4.70668781350371</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.34308820373625</v>
+        <v>4.377910814134251</v>
       </c>
       <c r="D2084" t="n">
         <v>-5.73902375098043</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.04712227903033</v>
+        <v>2.081944889428331</v>
       </c>
       <c r="F2084" t="n">
         <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.665519339123478</v>
+        <v>4.700341949521479</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342396881175246</v>
+        <v>4.377219491573246</v>
       </c>
       <c r="D2085" t="n">
         <v>-5.721264673477356</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.053534587470555</v>
+        <v>2.088357197868556</v>
       </c>
       <c r="F2085" t="n">
         <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.664828016562474</v>
+        <v>4.699650626960475</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355179067083832</v>
+        <v>4.390001677481833</v>
       </c>
       <c r="D2086" t="n">
         <v>-5.621634522428288</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.106168833798769</v>
+        <v>2.14099144419677</v>
       </c>
       <c r="F2086" t="n">
         <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.737388293100501</v>
+        <v>4.772210903498502</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544333332582559</v>
+        <v>4.57915594298056</v>
       </c>
       <c r="D2087" t="n">
         <v>-5.6710340311173</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.275563295821891</v>
+        <v>2.310385906219892</v>
       </c>
       <c r="F2087" t="n">
         <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.932697858658274</v>
+        <v>4.967520469056275</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.531522005685421</v>
+        <v>4.566344616083422</v>
       </c>
       <c r="D2088" t="n">
         <v>-5.464349557474923</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.345425758381703</v>
+        <v>2.380248368779704</v>
       </c>
       <c r="F2088" t="n">
         <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.043897215946562</v>
+        <v>5.078719826344563</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533523519339526</v>
+        <v>4.568346129737527</v>
       </c>
       <c r="D2089" t="n">
         <v>-5.49850645247245</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.333764514036798</v>
+        <v>2.368587124434799</v>
       </c>
       <c r="F2089" t="n">
         <v>0.7703749142277558</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.995748467876179</v>
+        <v>5.03057107827418</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.887020633329193</v>
+        <v>4.921843243727194</v>
       </c>
       <c r="D2090" t="n">
         <v>-5.405916973410993</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.724297419651048</v>
+        <v>2.759120030049049</v>
       </c>
       <c r="F2090" t="n">
         <v>0.7703749142277558</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.349245581865847</v>
+        <v>5.384068192263848</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.80905590510867</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891583744896296</v>
+        <v>4.926406355294297</v>
       </c>
       <c r="D2091" t="n">
         <v>-5.479077577184138</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.699596289708893</v>
+        <v>2.734418900106894</v>
       </c>
       <c r="F2091" t="n">
         <v>0.7423537141935128</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.336995973412405</v>
+        <v>5.371818583810406</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941413686219824</v>
+        <v>4.976236296617825</v>
       </c>
       <c r="D2092" t="n">
         <v>-5.426861267387796</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.770312754950957</v>
+        <v>2.805135365348958</v>
       </c>
       <c r="F2092" t="n">
         <v>0.7423537141935128</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.386825914735931</v>
+        <v>5.421648525133932</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950227656429835</v>
+        <v>4.985050266827836</v>
       </c>
       <c r="D2093" t="n">
         <v>-5.39496375030255</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.791885731995067</v>
+        <v>2.826708342393067</v>
       </c>
       <c r="F2093" t="n">
         <v>0.7742512312787586</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.41477839519709</v>
+        <v>5.449601005595091</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945865240469032</v>
+        <v>4.980687850867032</v>
       </c>
       <c r="D2094" t="n">
         <v>-5.409719074502691</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.781621186354208</v>
+        <v>2.816443796752208</v>
       </c>
       <c r="F2094" t="n">
         <v>0.7742512312787586</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.410415979236287</v>
+        <v>5.445238589634288</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936789743885312</v>
+        <v>4.971612354283312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.407580303646429</v>
+        <v>-5.360254451132779</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.773401198112992</v>
+        <v>2.827154149516453</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.776390002135021</v>
+        <v>0.8237158546486703</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.402623745166324</v>
+        <v>5.465841867072514</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933197411600246</v>
+        <v>4.968020021998247</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.244472311492814</v>
+        <v>-5.197146458979164</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.835052062689372</v>
+        <v>2.888805014092833</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9394979942886362</v>
+        <v>0.9868238468022855</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.496896208173428</v>
+        <v>5.560114330079618</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942244448291374</v>
+        <v>4.977067058689375</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.111664685995647</v>
+        <v>-5.064338833481997</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.897222149579367</v>
+        <v>2.950975100982828</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9394979942886362</v>
+        <v>0.9868238468022855</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.505943244864556</v>
+        <v>5.569161366770746</v>
       </c>
     </row>
     <row r="2098">
@@ -49802,19 +49802,19 @@
         <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.943101913277496</v>
+        <v>4.977924523675497</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.174372602470205</v>
+        <v>-5.127046749956556</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.872996447975666</v>
+        <v>2.926749399379126</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.8767900778140785</v>
+        <v>0.9241159303277278</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.469175959965943</v>
+        <v>5.532394081872133</v>
       </c>
     </row>
     <row r="2099">
@@ -49825,19 +49825,19 @@
         <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.906011330067848</v>
+        <v>4.940833940465849</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.126364478626512</v>
+        <v>-5.079038626112863</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.855109114303495</v>
+        <v>2.908862065706956</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.8767900778140785</v>
+        <v>0.9241159303277278</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.432085376756295</v>
+        <v>5.495303498662485</v>
       </c>
     </row>
     <row r="2100">
@@ -49848,19 +49848,19 @@
         <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.909943583625799</v>
+        <v>4.944766194023799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.047538821442922</v>
+        <v>-5.000212968929272</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.890571630734882</v>
+        <v>2.944324582138342</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.9556157349976689</v>
+        <v>1.002941587511318</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.4833130246244</v>
+        <v>5.54653114653059</v>
       </c>
     </row>
     <row r="2101">
@@ -49871,19 +49871,19 @@
         <v>3.868502531686404</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.904842676232835</v>
+        <v>4.939665286630836</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.855604020189048</v>
+        <v>-4.808278167675399</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.962244643843468</v>
+        <v>3.015997595246929</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.9556157349976689</v>
+        <v>1.002941587511318</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.478212117231437</v>
+        <v>5.541430239137627</v>
       </c>
     </row>
     <row r="2102">
@@ -49894,19 +49894,19 @@
         <v>3.84932404404671</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.900196585621931</v>
+        <v>4.935019196019931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.737430642171121</v>
+        <v>-4.690104789657472</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.004867904439734</v>
+        <v>3.058620855843195</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.073789113015596</v>
+        <v>1.121114965529245</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.544470053431288</v>
+        <v>5.607688175337479</v>
       </c>
     </row>
     <row r="2103">
@@ -49917,19 +49917,19 @@
         <v>3.836463274528999</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.929285178484958</v>
+        <v>4.964107788882958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.62401595938839</v>
+        <v>-4.57669010687474</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.079322370415854</v>
+        <v>3.133075321819314</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.187203795798327</v>
+        <v>1.234529648311977</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.641607455963954</v>
+        <v>5.704825577870144</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.756775366761264</v>
+        <v>3.749485587971754</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.922845401496135</v>
+        <v>4.957668011894135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.535542242145082</v>
+        <v>-4.549641069181487</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.108272080324354</v>
+        <v>3.137455159907793</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.275677513041635</v>
+        <v>1.26157868600523</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.688251909321116</v>
+        <v>5.714615223497274</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241002.xlsx
+++ b/tame_output/ON/bt/strategyON_20241002.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>113.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>184.1%</t>
+          <t>180.7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.4%</t>
+          <t>420.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-616.5%</t>
+          <t>-623.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-62.5%</t>
+          <t>-68.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.8%</t>
+          <t>-204.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-97.8%</t>
+          <t>-101.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>124.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>116.0%</t>
+          <t>113.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>119.8%</t>
         </is>
       </c>
     </row>
@@ -49250,19 +49250,19 @@
         <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.047942477975778</v>
+        <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.425076287933173</v>
+        <v>-5.490338191132929</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.877555538488761</v>
+        <v>1.816628166810858</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.5254966381482625</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.385066596594019</v>
+        <v>4.328417850466735</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.058106989020827</v>
+        <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.516458850498632</v>
+        <v>-5.581720753698387</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.851167024507627</v>
+        <v>1.790239652829724</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.4889317534289179</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.373292176807461</v>
+        <v>4.316643430680178</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.160235246845096</v>
+        <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.504752132511626</v>
+        <v>-5.570014035711381</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.957977969526697</v>
+        <v>1.897050597848795</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5006384714159243</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.482444465423933</v>
+        <v>4.42579571929665</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.1632675855765</v>
+        <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.575664206253903</v>
+        <v>-5.640926109453659</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.932645478761192</v>
+        <v>1.871718107083288</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5006384714159243</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.485476804155338</v>
+        <v>4.428828058028055</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.376172418854559</v>
+        <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.585980304420255</v>
+        <v>-5.651242207620011</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.141423872772709</v>
+        <v>2.080496501094805</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5006384714159243</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.698381637433396</v>
+        <v>4.641732891306113</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.375351085766648</v>
+        <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.585886336402882</v>
+        <v>-5.651148239602638</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.140640126891748</v>
+        <v>2.079712755213844</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5010083327632423</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.697782221153877</v>
+        <v>4.641133475026593</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.369583071711002</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.734252564059027</v>
+        <v>-5.799514467258783</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.075525621773644</v>
+        <v>2.01459825009574</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5010083327632423</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.69201420709823</v>
+        <v>4.635365460970947</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.369583071711002</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.733304140940988</v>
+        <v>-5.798566044140745</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.075904991020859</v>
+        <v>2.014977619342956</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5010083327632423</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.69201420709823</v>
+        <v>4.635365460970947</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.382310679692094</v>
+        <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.83357395890001</v>
+        <v>-5.898835862099766</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.048524671818342</v>
+        <v>1.987597300140439</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5010083327632423</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.704741815079323</v>
+        <v>4.648093068952039</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.384256678116482</v>
+        <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.827581712111198</v>
+        <v>-5.892843615310954</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.052867568958255</v>
+        <v>1.991940197280351</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5010083327632423</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.70668781350371</v>
+        <v>4.650039067376427</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.377910814134251</v>
+        <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.73902375098043</v>
+        <v>-5.804285654180187</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.081944889428331</v>
+        <v>2.021017517750427</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5010083327632423</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.700341949521479</v>
+        <v>4.643693203394196</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383088</v>
+        <v>3.735300721383086</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.377219491573246</v>
+        <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.721264673477356</v>
+        <v>-5.786526576677113</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.088357197868556</v>
+        <v>2.027429826190652</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5010083327632423</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.699650626960475</v>
+        <v>4.643001880833191</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720992</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.390001677481833</v>
+        <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.621634522428288</v>
+        <v>-5.686896425628045</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.14099144419677</v>
+        <v>2.080064072518867</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.6006384838123098</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.772210903498502</v>
+        <v>4.715562157371219</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.57915594298056</v>
+        <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.6710340311173</v>
+        <v>-5.736295934317056</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.310385906219892</v>
+        <v>2.249458534541989</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.6108973172440545</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.967520469056275</v>
+        <v>4.910871722928992</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.749078058963128</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.566344616083422</v>
+        <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.464349557474923</v>
+        <v>-5.52961146067468</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.380248368779704</v>
+        <v>2.319320997101801</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.8175817908864301</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.078719826344563</v>
+        <v>5.022071080217279</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.740284389162538</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.568346129737527</v>
+        <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.49850645247245</v>
+        <v>-5.563768355672206</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.368587124434799</v>
+        <v>2.307659752756896</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.7339980213456176</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.03057107827418</v>
+        <v>4.973922332146897</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652378</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.921843243727194</v>
+        <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.405916973410993</v>
+        <v>-5.471178876610749</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.759120030049049</v>
+        <v>2.698192658371145</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.7339980213456176</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.384068192263848</v>
+        <v>5.327419446136564</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.80905590510867</v>
+        <v>3.809055905108668</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.926406355294297</v>
+        <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.479077577184138</v>
+        <v>-5.544339480383894</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.734418900106894</v>
+        <v>2.673491528428991</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7059768213113746</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.371818583810406</v>
+        <v>5.315169837683121</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.835202441103559</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.976236296617825</v>
+        <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.426861267387796</v>
+        <v>-5.492123170587552</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.805135365348958</v>
+        <v>2.744207993671055</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7059768213113746</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.421648525133932</v>
+        <v>5.364999779006649</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.82182714704774</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.985050266827836</v>
+        <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.39496375030255</v>
+        <v>-5.460225653502307</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.826708342393067</v>
+        <v>2.765780970715164</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.7378743383966204</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.449601005595091</v>
+        <v>5.392952259467807</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650751</v>
+        <v>3.825268416650749</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.980687850867032</v>
+        <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.409719074502691</v>
+        <v>-5.474980977702447</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.816443796752208</v>
+        <v>2.755516425074305</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.7378743383966204</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.445238589634288</v>
+        <v>5.388589843507004</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135745</v>
+        <v>3.845044666135744</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.971612354283312</v>
+        <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.360254451132779</v>
+        <v>-5.425516354332536</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.827154149516453</v>
+        <v>2.766226777838549</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8237158546486703</v>
+        <v>0.7873389617665321</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.465841867072514</v>
+        <v>5.409193120945231</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479219</v>
+        <v>3.825931790479217</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.968020021998247</v>
+        <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.197146458979164</v>
+        <v>-5.26240836217892</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.888805014092833</v>
+        <v>2.82787764241493</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.9504469539201473</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.560114330079618</v>
+        <v>5.503465583952335</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844243</v>
+        <v>3.847096478844241</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.977067058689375</v>
+        <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.064338833481997</v>
+        <v>-5.129600736681754</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.950975100982828</v>
+        <v>2.890047729304925</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.9504469539201473</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.569161366770746</v>
+        <v>5.512512620643463</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790947</v>
+        <v>3.832425987790945</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.977924523675497</v>
+        <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.127046749956556</v>
+        <v>-5.192308653156312</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.926749399379126</v>
+        <v>2.865822027701223</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9241159303277278</v>
+        <v>0.8877390374455896</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.532394081872133</v>
+        <v>5.47574533574485</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578993</v>
+        <v>3.861579399578991</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.940833940465849</v>
+        <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.079038626112863</v>
+        <v>-5.144300529312619</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.908862065706956</v>
+        <v>2.847934694029052</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9241159303277278</v>
+        <v>0.8877390374455896</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.495303498662485</v>
+        <v>5.438654752535202</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629881</v>
+        <v>3.872253907629879</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.944766194023799</v>
+        <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.000212968929272</v>
+        <v>-5.065474872129029</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.944324582138342</v>
+        <v>2.883397210460439</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.002941587511318</v>
+        <v>0.96656469462918</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.54653114653059</v>
+        <v>5.489882400403307</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686404</v>
+        <v>3.868502531686402</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.939665286630836</v>
+        <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.808278167675399</v>
+        <v>-4.873540070875155</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.015997595246929</v>
+        <v>2.955070223569026</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.002941587511318</v>
+        <v>0.96656469462918</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.541430239137627</v>
+        <v>5.484781493010344</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.84932404404671</v>
+        <v>3.849324044046709</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.935019196019931</v>
+        <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.690104789657472</v>
+        <v>-4.755366692857228</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.058620855843195</v>
+        <v>2.997693484165292</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.121114965529245</v>
+        <v>1.084738072647107</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.607688175337479</v>
+        <v>5.551039429210196</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.836463274528999</v>
+        <v>3.836463274528997</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.964107788882958</v>
+        <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.57669010687474</v>
+        <v>-4.641952010074497</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.133075321819314</v>
+        <v>3.072147950141411</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.234529648311977</v>
+        <v>1.198152755429839</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.704825577870144</v>
+        <v>5.648176831742861</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.749485587971754</v>
+        <v>3.738607178494052</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.957668011894135</v>
+        <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.549641069181487</v>
+        <v>-4.614902972381243</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.137455159907793</v>
+        <v>3.07652778822989</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.26157868600523</v>
+        <v>1.225201793123092</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.714615223497274</v>
+        <v>5.657966477369991</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241002.xlsx
+++ b/tame_output/ON/bt/strategyON_20241002.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>112.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>180.7%</t>
+          <t>177.8%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>124.9%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>119.8%</t>
+          <t>42.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2104"/>
+  <dimension ref="A1:G2105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013422</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -49937,7 +49937,7 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.738607178494052</v>
+        <v>3.805501212984013</v>
       </c>
       <c r="C2104" t="n">
         <v>4.922845401496135</v>
@@ -49953,6 +49953,29 @@
       </c>
       <c r="G2104" t="n">
         <v>5.657966477369991</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="2" t="n">
+        <v>45567</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>3.736469824391928</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>4.894561286864488</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>-4.614902972381243</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>3.07652778822989</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>1.225201793123092</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>4.887625083850856</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241002.xlsx
+++ b/tame_output/ON/bt/strategyON_20241002.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>112.6%</t>
+          <t>115.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>177.8%</t>
+          <t>185.0%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.2%</t>
+          <t>421.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.1%</t>
+          <t>-623.6%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-68.6%</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.4%</t>
+          <t>-204.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-101.5%</t>
+          <t>-97.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013422</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.488859435328235</v>
+        <v>-5.55968501832012</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.720470740419408</v>
+        <v>1.692140507222654</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5835714754020119</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.305647772195139</v>
+        <v>-5.376473355187025</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.796186355136692</v>
+        <v>1.767856121939938</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5835714754020119</v>
@@ -49115,10 +49115,10 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.233926325181288</v>
+        <v>-5.304751908173174</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.807819340021609</v>
+        <v>1.779489106824855</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6552929224158626</v>
@@ -49138,10 +49138,10 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.211553299573582</v>
+        <v>-5.282378882565467</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.763684296185863</v>
+        <v>1.735354062989109</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6665486735287641</v>
@@ -49161,10 +49161,10 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.244569595484327</v>
+        <v>-5.315395178476212</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.935675982706921</v>
+        <v>1.907345749510167</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5971112968620125</v>
@@ -49184,10 +49184,10 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.233041959834718</v>
+        <v>-5.303867542826604</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.932208262795013</v>
+        <v>1.903878029598259</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6561119550633749</v>
@@ -49207,10 +49207,10 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.330383461177087</v>
+        <v>-5.401209044168972</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.896939774779855</v>
+        <v>1.8686095415831</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6116917728978866</v>
@@ -49230,10 +49230,10 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.416239490517054</v>
+        <v>-5.487065073508939</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.863848445236706</v>
+        <v>1.835518212039952</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5693157036717515</v>
@@ -49253,16 +49253,16 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.490338191132929</v>
+        <v>-5.495901870925058</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.816628166810858</v>
+        <v>1.814402694894006</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5254966381482625</v>
+        <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.328417850466735</v>
+        <v>4.350243986196018</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.581720753698387</v>
+        <v>-5.587284433490517</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.790239652829724</v>
+        <v>1.788014180912872</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4889317534289179</v>
+        <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.316643430680178</v>
+        <v>4.338469566409461</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.570014035711381</v>
+        <v>-5.575577715503511</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.897050597848795</v>
+        <v>1.894825125931943</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5006384714159243</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.42579571929665</v>
+        <v>4.447621855025933</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.640926109453659</v>
+        <v>-5.646489789245788</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.871718107083288</v>
+        <v>1.869492635166436</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5006384714159243</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.428828058028055</v>
+        <v>4.450654193757337</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.651242207620011</v>
+        <v>-5.65680588741214</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.080496501094805</v>
+        <v>2.078271029177954</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5006384714159243</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.641732891306113</v>
+        <v>4.663559027035395</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.651148239602638</v>
+        <v>-5.656711919394767</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.079712755213844</v>
+        <v>2.077487283296993</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5010083327632423</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.641133475026593</v>
+        <v>4.662959610755876</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.799514467258783</v>
+        <v>-5.805078147050912</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.01459825009574</v>
+        <v>2.012372778178888</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5010083327632423</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.635365460970947</v>
+        <v>4.65719159670023</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740919</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.798566044140745</v>
+        <v>-5.804129723932873</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.014977619342956</v>
+        <v>2.012752147426104</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5010083327632423</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.635365460970947</v>
+        <v>4.65719159670023</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.898835862099766</v>
+        <v>-5.904399541891895</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.987597300140439</v>
+        <v>1.985371828223588</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5010083327632423</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.648093068952039</v>
+        <v>4.669919204681322</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.892843615310954</v>
+        <v>-5.898407295103083</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.991940197280351</v>
+        <v>1.9897147253635</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5010083327632423</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.650039067376427</v>
+        <v>4.67186520310571</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.804285654180187</v>
+        <v>-5.809849333972315</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.021017517750427</v>
+        <v>2.018792045833576</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5010083327632423</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.643693203394196</v>
+        <v>4.665519339123478</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383086</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.786526576677113</v>
+        <v>-5.792090256469241</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.027429826190652</v>
+        <v>2.025204354273801</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5010083327632423</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.643001880833191</v>
+        <v>4.664828016562474</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720992</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.686896425628045</v>
+        <v>-5.692460105420174</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.080064072518867</v>
+        <v>2.077838600602015</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6006384838123098</v>
+        <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.715562157371219</v>
+        <v>4.737388293100501</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455267</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.736295934317056</v>
+        <v>-5.741859614109185</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.249458534541989</v>
+        <v>2.247233062625137</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6108973172440545</v>
+        <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.910871722928992</v>
+        <v>4.932697858658274</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963128</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.52961146067468</v>
+        <v>-5.535175140466809</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.319320997101801</v>
+        <v>2.317095525184949</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8175817908864301</v>
+        <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.022071080217279</v>
+        <v>5.043897215946562</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162538</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.563768355672206</v>
+        <v>-5.569332035464335</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.307659752756896</v>
+        <v>2.305434280840044</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7339980213456176</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.973922332146897</v>
+        <v>4.995748467876179</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652378</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.471178876610749</v>
+        <v>-5.476742556402878</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.698192658371145</v>
+        <v>2.695967186454294</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7339980213456176</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.327419446136564</v>
+        <v>5.349245581865847</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108668</v>
+        <v>3.80905590510867</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.544339480383894</v>
+        <v>-5.549903160176023</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.673491528428991</v>
+        <v>2.671266056512139</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7059768213113746</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.315169837683121</v>
+        <v>5.336995973412405</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103559</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.492123170587552</v>
+        <v>-5.497686850379681</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.744207993671055</v>
+        <v>2.741982521754204</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7059768213113746</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.364999779006649</v>
+        <v>5.386825914735931</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.82182714704774</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.460225653502307</v>
+        <v>-5.465789333294436</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.765780970715164</v>
+        <v>2.763555498798313</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7378743383966204</v>
+        <v>0.7742512312787586</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.392952259467807</v>
+        <v>5.41477839519709</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650749</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.474980977702447</v>
+        <v>-5.480544657494576</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.755516425074305</v>
+        <v>2.753290953157453</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7378743383966204</v>
+        <v>0.7742512312787586</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.388589843507004</v>
+        <v>5.410415979236287</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.425516354332536</v>
+        <v>-5.431080034124665</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.766226777838549</v>
+        <v>2.764001305921698</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.7873389617665321</v>
+        <v>0.8237158546486703</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.409193120945231</v>
+        <v>5.431019256674514</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479217</v>
+        <v>3.825931790479218</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.26240836217892</v>
+        <v>-5.267972041971049</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.82787764241493</v>
+        <v>2.825652170498079</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9504469539201473</v>
+        <v>0.9868238468022855</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.503465583952335</v>
+        <v>5.525291719681618</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844241</v>
+        <v>3.847096478844242</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.129600736681754</v>
+        <v>-5.135164416473883</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.890047729304925</v>
+        <v>2.887822257388073</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9504469539201473</v>
+        <v>0.9868238468022855</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.512512620643463</v>
+        <v>5.534338756372746</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790945</v>
+        <v>3.832425987790946</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.192308653156312</v>
+        <v>-5.197872332948441</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.865822027701223</v>
+        <v>2.863596555784372</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.8877390374455896</v>
+        <v>0.9241159303277278</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.47574533574485</v>
+        <v>5.497571471474132</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578991</v>
+        <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.144300529312619</v>
+        <v>-5.149864209104748</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.847934694029052</v>
+        <v>2.845709222112201</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.8877390374455896</v>
+        <v>0.9241159303277278</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.438654752535202</v>
+        <v>5.460480888264485</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629879</v>
+        <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.065474872129029</v>
+        <v>-5.071038551921157</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.883397210460439</v>
+        <v>2.881171738543588</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.96656469462918</v>
+        <v>1.002941587511318</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.489882400403307</v>
+        <v>5.511708536132589</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686402</v>
+        <v>3.868502531686404</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.873540070875155</v>
+        <v>-4.879103750667284</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.955070223569026</v>
+        <v>2.952844751652174</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.96656469462918</v>
+        <v>1.002941587511318</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.484781493010344</v>
+        <v>5.506607628739626</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.849324044046709</v>
+        <v>3.84932404404671</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.755366692857228</v>
+        <v>-4.760930372649357</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.997693484165292</v>
+        <v>2.99546801224844</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.084738072647107</v>
+        <v>1.121114965529245</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.551039429210196</v>
+        <v>5.572865564939478</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.836463274528997</v>
+        <v>3.836463274528999</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.641952010074497</v>
+        <v>-4.647515689866625</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.072147950141411</v>
+        <v>3.06992247822456</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.198152755429839</v>
+        <v>1.234529648311977</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.648176831742861</v>
+        <v>5.670002967472143</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.805501212984013</v>
+        <v>3.805501212984015</v>
       </c>
       <c r="C2104" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.614902972381243</v>
+        <v>-4.620466652173372</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.07652778822989</v>
+        <v>3.074302316313038</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.225201793123092</v>
+        <v>1.26157868600523</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.657966477369991</v>
+        <v>5.679792613099274</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.736469824391928</v>
+        <v>3.835109089589306</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.894561286864488</v>
+        <v>4.966617527008364</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.614902972381243</v>
+        <v>-4.620466652173372</v>
       </c>
       <c r="E2105" t="n">
-        <v>3.07652778822989</v>
+        <v>3.074302316313038</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.225201793123092</v>
+        <v>1.26157868600523</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.887625083850856</v>
+        <v>4.959681323994732</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241002.xlsx
+++ b/tame_output/ON/bt/strategyON_20241002.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>43.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>115.3%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>185.0%</t>
+          <t>175.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-43.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.4%</t>
+          <t>420.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.6%</t>
+          <t>-642.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>-76.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.8%</t>
+          <t>-206.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-97.8%</t>
+          <t>-112.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>40.1%</t>
         </is>
       </c>
     </row>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013422</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48655,10 +48655,10 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.059187351780725</v>
+        <v>-5.170262148601734</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.564450737282303</v>
+        <v>1.520020818553899</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6030277491990641</v>
@@ -48678,10 +48678,10 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.23429418435717</v>
+        <v>-5.345368981178179</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.454659917845192</v>
+        <v>1.410229999116788</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6030277491990641</v>
@@ -48701,10 +48701,10 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.038194030926647</v>
+        <v>-5.149268827747656</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.540122598214341</v>
+        <v>1.495692679485937</v>
       </c>
       <c r="F2050" t="n">
         <v>0.799127902629587</v>
@@ -48724,10 +48724,10 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.885168638813362</v>
+        <v>-4.996243435634372</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.700503754632559</v>
+        <v>1.656073835904155</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9521532947428711</v>
@@ -48747,10 +48747,10 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.913475952686633</v>
+        <v>-5.024550749507642</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.876647053991543</v>
+        <v>1.83221713526314</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9521532947428711</v>
@@ -48770,10 +48770,10 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.080069177800155</v>
+        <v>-5.191143974621165</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.779412715300217</v>
+        <v>1.734982796571813</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7855600696293488</v>
@@ -48793,10 +48793,10 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.057033384438589</v>
+        <v>-5.168108181259599</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.792303435306561</v>
+        <v>1.747873516578157</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7855600696293488</v>
@@ -48816,10 +48816,10 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.027787403982892</v>
+        <v>-5.138862200803902</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.801619882612335</v>
+        <v>1.757189963883931</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7855600696293488</v>
@@ -48839,10 +48839,10 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.134712951860744</v>
+        <v>-5.245787748681753</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.75614290261883</v>
+        <v>1.711712983890426</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6786345217514974</v>
@@ -48862,10 +48862,10 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.279731510367992</v>
+        <v>-5.390806307189002</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.699564281359164</v>
+        <v>1.655134362630761</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5336159632442489</v>
@@ -48885,10 +48885,10 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.39807327615271</v>
+        <v>-5.509148072973719</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.75215881430303</v>
+        <v>1.707728895574627</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5443020018071389</v>
@@ -48908,10 +48908,10 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.449483698473418</v>
+        <v>-5.560558495294427</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.729380342500686</v>
+        <v>1.684950423772283</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5443020018071389</v>
@@ -48931,10 +48931,10 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.528903149681169</v>
+        <v>-5.639977946502179</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.697515690091875</v>
+        <v>1.653085771363471</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5443020018071389</v>
@@ -48954,10 +48954,10 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.624366147598387</v>
+        <v>-5.735440944419397</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.659324384483031</v>
+        <v>1.614894465754627</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5443020018071389</v>
@@ -48977,10 +48977,10 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.559990236747672</v>
+        <v>-5.671065033568682</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.683171145385927</v>
+        <v>1.638741226657524</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6086779126578541</v>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.615359398879866</v>
+        <v>-5.726434195700875</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.666757298280777</v>
+        <v>1.622327379552373</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6086779126578541</v>
@@ -49023,10 +49023,10 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.633577865877474</v>
+        <v>-5.744652662698484</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.659008274824666</v>
+        <v>1.614578356096262</v>
       </c>
       <c r="F2064" t="n">
         <v>0.5835714754020119</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.594894430533544</v>
+        <v>-5.705969227354553</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.694356041812557</v>
+        <v>1.649926123084153</v>
       </c>
       <c r="F2065" t="n">
         <v>0.5835714754020119</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.55968501832012</v>
+        <v>-5.599934232149244</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.692140507222654</v>
+        <v>1.676040821691004</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5835714754020119</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.376473355187025</v>
+        <v>-5.416722569016149</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.767856121939938</v>
+        <v>1.751756436408288</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5835714754020119</v>
@@ -49115,10 +49115,10 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.304751908173174</v>
+        <v>-5.345001122002298</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.779489106824855</v>
+        <v>1.763389421293205</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6552929224158626</v>
@@ -49138,10 +49138,10 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.282378882565467</v>
+        <v>-5.322628096394592</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.735354062989109</v>
+        <v>1.719254377457459</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6665486735287641</v>
@@ -49161,10 +49161,10 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.315395178476212</v>
+        <v>-5.355644392305337</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.907345749510167</v>
+        <v>1.891246063978517</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5971112968620125</v>
@@ -49184,10 +49184,10 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.303867542826604</v>
+        <v>-5.344116756655728</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.903878029598259</v>
+        <v>1.887778344066609</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6561119550633749</v>
@@ -49207,10 +49207,10 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.401209044168972</v>
+        <v>-5.441458257998097</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.8686095415831</v>
+        <v>1.852509856051451</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6116917728978866</v>
@@ -49230,10 +49230,10 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.487065073508939</v>
+        <v>-5.527314287338063</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.835518212039952</v>
+        <v>1.819418526508302</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5693157036717515</v>
@@ -49253,10 +49253,10 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.495901870925058</v>
+        <v>-5.536151084754183</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.814402694894006</v>
+        <v>1.798303009362356</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5618735310304008</v>
@@ -49276,10 +49276,10 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.587284433490517</v>
+        <v>-5.627533647319641</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.788014180912872</v>
+        <v>1.771914495381222</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5253086463110561</v>
@@ -49299,10 +49299,10 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.575577715503511</v>
+        <v>-5.615826929332635</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.894825125931943</v>
+        <v>1.878725440400293</v>
       </c>
       <c r="F2076" t="n">
         <v>0.5370153642980625</v>
@@ -49322,10 +49322,10 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.646489789245788</v>
+        <v>-5.686739003074912</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.869492635166436</v>
+        <v>1.853392949634787</v>
       </c>
       <c r="F2077" t="n">
         <v>0.5370153642980625</v>
@@ -49345,10 +49345,10 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.65680588741214</v>
+        <v>-5.697055101241264</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.078271029177954</v>
+        <v>2.062171343646304</v>
       </c>
       <c r="F2078" t="n">
         <v>0.5370153642980625</v>
@@ -49362,16 +49362,16 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.656711919394767</v>
+        <v>-5.696961133223891</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.077487283296993</v>
+        <v>2.061387597765343</v>
       </c>
       <c r="F2079" t="n">
         <v>0.5373852256453805</v>
@@ -49391,10 +49391,10 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.805078147050912</v>
+        <v>-5.845327360880036</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.012372778178888</v>
+        <v>1.996273092647239</v>
       </c>
       <c r="F2080" t="n">
         <v>0.5373852256453805</v>
@@ -49408,16 +49408,16 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.804129723932873</v>
+        <v>-5.844378937761998</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.012752147426104</v>
+        <v>1.996652461894454</v>
       </c>
       <c r="F2081" t="n">
         <v>0.5373852256453805</v>
@@ -49431,16 +49431,16 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.904399541891895</v>
+        <v>-5.944648755721019</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.985371828223588</v>
+        <v>1.969272142691938</v>
       </c>
       <c r="F2082" t="n">
         <v>0.5373852256453805</v>
@@ -49454,16 +49454,16 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.898407295103083</v>
+        <v>-5.938656508932207</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.9897147253635</v>
+        <v>1.97361503983185</v>
       </c>
       <c r="F2083" t="n">
         <v>0.5373852256453805</v>
@@ -49477,16 +49477,16 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.809849333972315</v>
+        <v>-5.85009854780144</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.018792045833576</v>
+        <v>2.002692360301926</v>
       </c>
       <c r="F2084" t="n">
         <v>0.5373852256453805</v>
@@ -49500,16 +49500,16 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383088</v>
+        <v>3.735300721383086</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.792090256469241</v>
+        <v>-5.832339470298366</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.025204354273801</v>
+        <v>2.009104668742151</v>
       </c>
       <c r="F2085" t="n">
         <v>0.5373852256453805</v>
@@ -49523,16 +49523,16 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720992</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.692460105420174</v>
+        <v>-5.732709319249298</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.077838600602015</v>
+        <v>2.061738915070365</v>
       </c>
       <c r="F2086" t="n">
         <v>0.637015376694448</v>
@@ -49546,16 +49546,16 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.741859614109185</v>
+        <v>-5.782108827938309</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.247233062625137</v>
+        <v>2.231133377093487</v>
       </c>
       <c r="F2087" t="n">
         <v>0.6472742101261927</v>
@@ -49569,16 +49569,16 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.749078058963128</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.535175140466809</v>
+        <v>-5.575424354295933</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.317095525184949</v>
+        <v>2.3009958396533</v>
       </c>
       <c r="F2088" t="n">
         <v>0.8539586837685683</v>
@@ -49592,16 +49592,16 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.740284389162538</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.569332035464335</v>
+        <v>-5.609581249293459</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.305434280840044</v>
+        <v>2.289334595308394</v>
       </c>
       <c r="F2089" t="n">
         <v>0.7703749142277558</v>
@@ -49615,16 +49615,16 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652378</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.476742556402878</v>
+        <v>-5.516991770232003</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.695967186454294</v>
+        <v>2.679867500922644</v>
       </c>
       <c r="F2090" t="n">
         <v>0.7703749142277558</v>
@@ -49638,16 +49638,16 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.80905590510867</v>
+        <v>3.809055905108668</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.549903160176023</v>
+        <v>-5.590152374005148</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.671266056512139</v>
+        <v>2.655166370980489</v>
       </c>
       <c r="F2091" t="n">
         <v>0.7423537141935128</v>
@@ -49661,16 +49661,16 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.835202441103559</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.497686850379681</v>
+        <v>-5.537936064208806</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.741982521754204</v>
+        <v>2.725882836222554</v>
       </c>
       <c r="F2092" t="n">
         <v>0.7423537141935128</v>
@@ -49684,16 +49684,16 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.82182714704774</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.465789333294436</v>
+        <v>-5.50603854712356</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.763555498798313</v>
+        <v>2.747455813266663</v>
       </c>
       <c r="F2093" t="n">
         <v>0.7742512312787586</v>
@@ -49707,16 +49707,16 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650751</v>
+        <v>3.825268416650749</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.480544657494576</v>
+        <v>-5.520793871323701</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.753290953157453</v>
+        <v>2.737191267625803</v>
       </c>
       <c r="F2094" t="n">
         <v>0.7742512312787586</v>
@@ -49736,10 +49736,10 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.431080034124665</v>
+        <v>-5.471329247953789</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.764001305921698</v>
+        <v>2.747901620390048</v>
       </c>
       <c r="F2095" t="n">
         <v>0.8237158546486703</v>
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479218</v>
+        <v>3.825931790479217</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.267972041971049</v>
+        <v>-5.455047435973963</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.825652170498079</v>
+        <v>2.750822012896913</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.8399976666284958</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.525291719681618</v>
+        <v>5.437196011577344</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844242</v>
+        <v>3.847096478844241</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.135164416473883</v>
+        <v>-5.322239810476797</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.887822257388073</v>
+        <v>2.812992099786908</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9868238468022855</v>
+        <v>0.8399976666284958</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.534338756372746</v>
+        <v>5.446243048268472</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790946</v>
+        <v>3.832425987790945</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.197872332948441</v>
+        <v>-5.384947726951355</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.863596555784372</v>
+        <v>2.788766398183206</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9241159303277278</v>
+        <v>0.7772897501539381</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.497571471474132</v>
+        <v>5.409475763369858</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578993</v>
+        <v>3.861579399578991</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.149864209104748</v>
+        <v>-5.336939603107662</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.845709222112201</v>
+        <v>2.770879064511035</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9241159303277278</v>
+        <v>0.7772897501539381</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.460480888264485</v>
+        <v>5.372385180160212</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629881</v>
+        <v>3.872253907629879</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.071038551921157</v>
+        <v>-5.258113945924071</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.881171738543588</v>
+        <v>2.806341580942422</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.002941587511318</v>
+        <v>0.8561154073375286</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.511708536132589</v>
+        <v>5.423612828028316</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686404</v>
+        <v>3.868502531686402</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.879103750667284</v>
+        <v>-5.066179144670198</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.952844751652174</v>
+        <v>2.878014594051008</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.002941587511318</v>
+        <v>0.8561154073375286</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.506607628739626</v>
+        <v>5.418511920635352</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.84932404404671</v>
+        <v>3.849324044046709</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.760930372649357</v>
+        <v>-4.948005766652271</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.99546801224844</v>
+        <v>2.920637854647274</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.121114965529245</v>
+        <v>0.9742887853554558</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.572865564939478</v>
+        <v>5.484769856835205</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.836463274528999</v>
+        <v>3.836463274528997</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.647515689866625</v>
+        <v>-4.834591083869539</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.06992247822456</v>
+        <v>2.995092320623394</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.234529648311977</v>
+        <v>1.087703468138187</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.670002967472143</v>
+        <v>5.58190725936787</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.805501212984015</v>
+        <v>3.805501212984013</v>
       </c>
       <c r="C2104" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.620466652173372</v>
+        <v>-4.807542046176286</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.074302316313038</v>
+        <v>2.999472158711872</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.26157868600523</v>
+        <v>1.114752505831441</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.679792613099274</v>
+        <v>5.591696904995</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.835109089589306</v>
+        <v>3.712362311670565</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.966617527008364</v>
+        <v>4.868369187433481</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.620466652173372</v>
+        <v>-4.807542046176286</v>
       </c>
       <c r="E2105" t="n">
-        <v>3.074302316313038</v>
+        <v>2.999472158711872</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.26157868600523</v>
+        <v>1.114752505831441</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.959681323994732</v>
+        <v>4.861432984419849</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241002.xlsx
+++ b/tame_output/ON/bt/strategyON_20241002.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>175.2%</t>
+          <t>171.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-43.7%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.0%</t>
+          <t>419.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-642.3%</t>
+          <t>-630.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-71.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-206.2%</t>
+          <t>-203.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-112.5%</t>
+          <t>-105.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
     </row>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013422</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.170262148601734</v>
+        <v>-5.059187351780725</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.520020818553899</v>
+        <v>1.564450737282303</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6030277491990641</v>
@@ -48678,10 +48678,10 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.345368981178179</v>
+        <v>-5.23429418435717</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.410229999116788</v>
+        <v>1.454659917845192</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6030277491990641</v>
@@ -48701,10 +48701,10 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.149268827747656</v>
+        <v>-5.038194030926647</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.495692679485937</v>
+        <v>1.540122598214341</v>
       </c>
       <c r="F2050" t="n">
         <v>0.799127902629587</v>
@@ -48724,10 +48724,10 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.996243435634372</v>
+        <v>-4.885168638813362</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.656073835904155</v>
+        <v>1.700503754632559</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9521532947428711</v>
@@ -48747,10 +48747,10 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.024550749507642</v>
+        <v>-4.913475952686633</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.83221713526314</v>
+        <v>1.876647053991543</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9521532947428711</v>
@@ -48770,10 +48770,10 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.191143974621165</v>
+        <v>-5.080069177800155</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.734982796571813</v>
+        <v>1.779412715300217</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7855600696293488</v>
@@ -48793,10 +48793,10 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.168108181259599</v>
+        <v>-5.057033384438589</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.747873516578157</v>
+        <v>1.792303435306561</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7855600696293488</v>
@@ -48816,10 +48816,10 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.138862200803902</v>
+        <v>-5.027787403982892</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.757189963883931</v>
+        <v>1.801619882612335</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7855600696293488</v>
@@ -48839,10 +48839,10 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.245787748681753</v>
+        <v>-5.134712951860744</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.711712983890426</v>
+        <v>1.75614290261883</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6786345217514974</v>
@@ -48862,10 +48862,10 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.390806307189002</v>
+        <v>-5.279731510367992</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.655134362630761</v>
+        <v>1.699564281359164</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5336159632442489</v>
@@ -48885,10 +48885,10 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.509148072973719</v>
+        <v>-5.39807327615271</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.707728895574627</v>
+        <v>1.75215881430303</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5443020018071389</v>
@@ -48908,10 +48908,10 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.560558495294427</v>
+        <v>-5.449483698473418</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.684950423772283</v>
+        <v>1.729380342500686</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5443020018071389</v>
@@ -48931,10 +48931,10 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.639977946502179</v>
+        <v>-5.528903149681169</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.653085771363471</v>
+        <v>1.697515690091875</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5443020018071389</v>
@@ -48954,10 +48954,10 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.735440944419397</v>
+        <v>-5.624366147598387</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.614894465754627</v>
+        <v>1.659324384483031</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5443020018071389</v>
@@ -48977,10 +48977,10 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.671065033568682</v>
+        <v>-5.559990236747672</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.638741226657524</v>
+        <v>1.683171145385927</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6086779126578541</v>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.726434195700875</v>
+        <v>-5.615359398879866</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.622327379552373</v>
+        <v>1.666757298280777</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6086779126578541</v>
@@ -49023,10 +49023,10 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.744652662698484</v>
+        <v>-5.633577865877474</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.614578356096262</v>
+        <v>1.659008274824666</v>
       </c>
       <c r="F2064" t="n">
         <v>0.5835714754020119</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.705969227354553</v>
+        <v>-5.594894430533544</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.649926123084153</v>
+        <v>1.694356041812557</v>
       </c>
       <c r="F2065" t="n">
         <v>0.5835714754020119</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.599934232149244</v>
+        <v>-5.488859435328235</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.676040821691004</v>
+        <v>1.720470740419408</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5835714754020119</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.416722569016149</v>
+        <v>-5.305647772195139</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.751756436408288</v>
+        <v>1.796186355136692</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5835714754020119</v>
@@ -49115,10 +49115,10 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.345001122002298</v>
+        <v>-5.233926325181288</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.763389421293205</v>
+        <v>1.807819340021609</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6552929224158626</v>
@@ -49138,10 +49138,10 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.322628096394592</v>
+        <v>-5.211553299573582</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.719254377457459</v>
+        <v>1.763684296185863</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6665486735287641</v>
@@ -49161,10 +49161,10 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.355644392305337</v>
+        <v>-5.244569595484327</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.891246063978517</v>
+        <v>1.935675982706921</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5971112968620125</v>
@@ -49184,10 +49184,10 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.344116756655728</v>
+        <v>-5.233041959834718</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.887778344066609</v>
+        <v>1.932208262795013</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6561119550633749</v>
@@ -49207,10 +49207,10 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.441458257998097</v>
+        <v>-5.330383461177087</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.852509856051451</v>
+        <v>1.896939774779855</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6116917728978866</v>
@@ -49230,10 +49230,10 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.527314287338063</v>
+        <v>-5.416239490517054</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.819418526508302</v>
+        <v>1.863848445236706</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5693157036717515</v>
@@ -49253,10 +49253,10 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.536151084754183</v>
+        <v>-5.425076287933173</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.798303009362356</v>
+        <v>1.84273292809076</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5618735310304008</v>
@@ -49276,10 +49276,10 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.627533647319641</v>
+        <v>-5.516458850498632</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.771914495381222</v>
+        <v>1.816344414109626</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5253086463110561</v>
@@ -49299,10 +49299,10 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.615826929332635</v>
+        <v>-5.504752132511626</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.878725440400293</v>
+        <v>1.923155359128697</v>
       </c>
       <c r="F2076" t="n">
         <v>0.5370153642980625</v>
@@ -49322,10 +49322,10 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.686739003074912</v>
+        <v>-5.575664206253903</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.853392949634787</v>
+        <v>1.897822868363191</v>
       </c>
       <c r="F2077" t="n">
         <v>0.5370153642980625</v>
@@ -49345,10 +49345,10 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.697055101241264</v>
+        <v>-5.585980304420255</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.062171343646304</v>
+        <v>2.106601262374708</v>
       </c>
       <c r="F2078" t="n">
         <v>0.5370153642980625</v>
@@ -49368,16 +49368,16 @@
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.696961133223891</v>
+        <v>-5.722388099377723</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.061387597765343</v>
+        <v>2.05121681130381</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4646687762232421</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.662959610755876</v>
+        <v>4.619329741102593</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.845327360880036</v>
+        <v>-5.870754327033868</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.996273092647239</v>
+        <v>1.986102306185706</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4646687762232421</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.65719159670023</v>
+        <v>4.613561727046947</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.844378937761998</v>
+        <v>-5.86980590391583</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.996652461894454</v>
+        <v>1.986481675432922</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4646687762232421</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.65719159670023</v>
+        <v>4.613561727046947</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.944648755721019</v>
+        <v>-5.970075721874851</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.969272142691938</v>
+        <v>1.959101356230405</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4646687762232421</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.669919204681322</v>
+        <v>4.626289335028039</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.938656508932207</v>
+        <v>-5.964083475086039</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.97361503983185</v>
+        <v>1.963444253370317</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4646687762232421</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.67186520310571</v>
+        <v>4.628235333452427</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.85009854780144</v>
+        <v>-5.875525513955272</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.002692360301926</v>
+        <v>1.992521573840393</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4646687762232421</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.665519339123478</v>
+        <v>4.621889469470196</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.832339470298366</v>
+        <v>-5.857766436452198</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.009104668742151</v>
+        <v>1.998933882280618</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.4646687762232421</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.664828016562474</v>
+        <v>4.621198146909191</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.732709319249298</v>
+        <v>-5.75813628540313</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.061738915070365</v>
+        <v>2.051568128608833</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.5642989272723096</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.737388293100501</v>
+        <v>4.693758423447218</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.782108827938309</v>
+        <v>-5.807535794092141</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.231133377093487</v>
+        <v>2.220962590631955</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.5745577607040543</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.932697858658274</v>
+        <v>4.889067989004992</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.575424354295933</v>
+        <v>-5.600851320449765</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.3009958396533</v>
+        <v>2.290825053191767</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.7812422343464299</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.043897215946562</v>
+        <v>5.000267346293279</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.609581249293459</v>
+        <v>-5.635008215447291</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.289334595308394</v>
+        <v>2.279163808846862</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.6976584648056174</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.995748467876179</v>
+        <v>4.952118598222897</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.516991770232003</v>
+        <v>-5.542418736385835</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.679867500922644</v>
+        <v>2.669696714461111</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.6976584648056174</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.349245581865847</v>
+        <v>5.305615712212564</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.590152374005148</v>
+        <v>-5.61557934015898</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.655166370980489</v>
+        <v>2.644995584518957</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.6696372647713744</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.336995973412405</v>
+        <v>5.293366103759121</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.537936064208806</v>
+        <v>-5.563363030362638</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.725882836222554</v>
+        <v>2.715712049761021</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.6696372647713744</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.386825914735931</v>
+        <v>5.343196045082649</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.50603854712356</v>
+        <v>-5.531465513277392</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.747455813266663</v>
+        <v>2.73728502680513</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.7015347818566202</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.41477839519709</v>
+        <v>5.371148525543807</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.520793871323701</v>
+        <v>-5.546220837477533</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.737191267625803</v>
+        <v>2.727020481164271</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7742512312787586</v>
+        <v>0.7015347818566202</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.410415979236287</v>
+        <v>5.366786109583004</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.471329247953789</v>
+        <v>-5.496756214107621</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.747901620390048</v>
+        <v>2.737730833928515</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8237158546486703</v>
+        <v>0.7509994052265319</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.431019256674514</v>
+        <v>5.387389387021231</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.455047435973963</v>
+        <v>-5.333648221954006</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.750822012896913</v>
+        <v>2.799381698504896</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.8399976666284958</v>
+        <v>0.9141073973801471</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.437196011577344</v>
+        <v>5.481661850028335</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.322239810476797</v>
+        <v>-5.200840596456839</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.812992099786908</v>
+        <v>2.861551785394891</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.8399976666284958</v>
+        <v>0.9141073973801471</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.446243048268472</v>
+        <v>5.490708886719463</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.384947726951355</v>
+        <v>-5.263548512931397</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.788766398183206</v>
+        <v>2.837326083791189</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.7772897501539381</v>
+        <v>0.8513994809055894</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.409475763369858</v>
+        <v>5.45394160182085</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.336939603107662</v>
+        <v>-5.215540389087704</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.770879064511035</v>
+        <v>2.819438750119018</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.7772897501539381</v>
+        <v>0.8513994809055894</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.372385180160212</v>
+        <v>5.416851018611202</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.258113945924071</v>
+        <v>-5.136714731904114</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.806341580942422</v>
+        <v>2.854901266550405</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.8561154073375286</v>
+        <v>0.9302251380891798</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.423612828028316</v>
+        <v>5.468078666479307</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.066179144670198</v>
+        <v>-4.94477993065024</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.878014594051008</v>
+        <v>2.926574279658992</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.8561154073375286</v>
+        <v>0.9302251380891798</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.418511920635352</v>
+        <v>5.462977759086344</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.948005766652271</v>
+        <v>-4.826606552632313</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.920637854647274</v>
+        <v>2.969197540255258</v>
       </c>
       <c r="F2102" t="n">
-        <v>0.9742887853554558</v>
+        <v>1.048398516107107</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.484769856835205</v>
+        <v>5.529235695286195</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.834591083869539</v>
+        <v>-4.713191869849582</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.995092320623394</v>
+        <v>3.043652006231377</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.087703468138187</v>
+        <v>1.161813198889838</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.58190725936787</v>
+        <v>5.626373097818861</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.805501212984013</v>
+        <v>3.805501212984012</v>
       </c>
       <c r="C2104" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.807542046176286</v>
+        <v>-4.686142832156328</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.999472158711872</v>
+        <v>3.048031844319856</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.114752505831441</v>
+        <v>1.188862236583092</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.591696904995</v>
+        <v>5.63616274344599</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.712362311670565</v>
+        <v>3.679388954063188</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.868369187433481</v>
+        <v>4.826763368481769</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.807542046176286</v>
+        <v>-4.686142832156328</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.999472158711872</v>
+        <v>3.048031844319856</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.114752505831441</v>
+        <v>1.188862236583092</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.861432984419849</v>
+        <v>4.819827165468137</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241002.xlsx
+++ b/tame_output/ON/bt/strategyON_20241002.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>112.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>171.0%</t>
+          <t>177.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.4%</t>
+          <t>419.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.2%</t>
+          <t>-623.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-72.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-105.1%</t>
+          <t>-98.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>118.1%</t>
         </is>
       </c>
     </row>
@@ -49963,19 +49963,19 @@
         <v>3.679388954063188</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.826763368481769</v>
+        <v>4.888333718867176</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.686142832156328</v>
+        <v>-4.620743799895498</v>
       </c>
       <c r="E2105" t="n">
-        <v>3.048031844319856</v>
+        <v>3.039679774595228</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.188862236583092</v>
+        <v>1.254261268843922</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.819827165468137</v>
+        <v>5.640890480173529</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241002.xlsx
+++ b/tame_output/ON/bt/strategyON_20241002.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.5%</t>
+          <t>419.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.6%</t>
+          <t>-621.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-71.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-203.9%</t>
+          <t>-204.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-98.6%</t>
+          <t>-97.2%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>118.9%</t>
         </is>
       </c>
     </row>
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.722388099377723</v>
+        <v>-5.585886336402882</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.05121681130381</v>
+        <v>2.105817516493747</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.4646687762232421</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.619329741102593</v>
+        <v>4.662959610755876</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.870754327033868</v>
+        <v>-5.72235642899768</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.986102306185706</v>
+        <v>2.045461465400181</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.4646687762232421</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.613561727046947</v>
+        <v>4.65719159670023</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.86980590391583</v>
+        <v>-5.721408005879642</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.986481675432922</v>
+        <v>2.045840834647397</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.4646687762232421</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.613561727046947</v>
+        <v>4.65719159670023</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.970075721874851</v>
+        <v>-5.821677823838662</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.959101356230405</v>
+        <v>2.01846051544488</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.4646687762232421</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.626289335028039</v>
+        <v>4.669919204681322</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.964083475086039</v>
+        <v>-5.815685577049851</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.963444253370317</v>
+        <v>2.022803412584793</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.4646687762232421</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.628235333452427</v>
+        <v>4.67186520310571</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.875525513955272</v>
+        <v>-5.727127615919083</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.992521573840393</v>
+        <v>2.051880733054869</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.4646687762232421</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.621889469470196</v>
+        <v>4.665519339123478</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383086</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.857766436452198</v>
+        <v>-5.709368538416009</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.998933882280618</v>
+        <v>2.058293041495094</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.4646687762232421</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.621198146909191</v>
+        <v>4.664828016562474</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720992</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.75813628540313</v>
+        <v>-5.609738387366941</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.051568128608833</v>
+        <v>2.110927287823308</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.5642989272723096</v>
+        <v>0.637015376694448</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.693758423447218</v>
+        <v>4.737388293100501</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455267</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.807535794092141</v>
+        <v>-5.659137896055952</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.220962590631955</v>
+        <v>2.28032174984643</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.5745577607040543</v>
+        <v>0.6472742101261927</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.889067989004992</v>
+        <v>4.932697858658274</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963128</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.600851320449765</v>
+        <v>-5.452453422413576</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.290825053191767</v>
+        <v>2.350184212406242</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.7812422343464299</v>
+        <v>0.8539586837685683</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.000267346293279</v>
+        <v>5.043897215946562</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162538</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.635008215447291</v>
+        <v>-5.486610317411102</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.279163808846862</v>
+        <v>2.338522968061337</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.6976584648056174</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.952118598222897</v>
+        <v>4.995748467876179</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652378</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.542418736385835</v>
+        <v>-5.394020838349646</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.669696714461111</v>
+        <v>2.729055873675587</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.6976584648056174</v>
+        <v>0.7703749142277558</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.305615712212564</v>
+        <v>5.349245581865847</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108668</v>
+        <v>3.80905590510867</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.61557934015898</v>
+        <v>-5.467181442122791</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.644995584518957</v>
+        <v>2.704354743733432</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.6696372647713744</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.293366103759121</v>
+        <v>5.336995973412405</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103559</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.563363030362638</v>
+        <v>-5.414965132326449</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.715712049761021</v>
+        <v>2.775071208975497</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.6696372647713744</v>
+        <v>0.7423537141935128</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.343196045082649</v>
+        <v>5.386825914735931</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.82182714704774</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.531465513277392</v>
+        <v>-5.383067615241203</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.73728502680513</v>
+        <v>2.796644186019606</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7015347818566202</v>
+        <v>0.7742512312787586</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.371148525543807</v>
+        <v>5.41477839519709</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650749</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.546220837477533</v>
+        <v>-5.397822939441344</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.727020481164271</v>
+        <v>2.786379640378746</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7015347818566202</v>
+        <v>0.7742512312787586</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.366786109583004</v>
+        <v>5.410415979236287</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135744</v>
+        <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.496756214107621</v>
+        <v>-5.348358316071432</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.737730833928515</v>
+        <v>2.797089993142991</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.7509994052265319</v>
+        <v>0.8237158546486703</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.387389387021231</v>
+        <v>5.431019256674514</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479217</v>
+        <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.333648221954006</v>
+        <v>-5.185250323917817</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.799381698504896</v>
+        <v>2.858740857719372</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9141073973801471</v>
+        <v>0.9868238468022855</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.481661850028335</v>
+        <v>5.525291719681618</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844241</v>
+        <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.200840596456839</v>
+        <v>-5.167919399785289</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.861551785394891</v>
+        <v>2.874720264063511</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9141073973801471</v>
+        <v>0.9868238468022855</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.490708886719463</v>
+        <v>5.534338756372746</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790945</v>
+        <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.263548512931397</v>
+        <v>-5.230627316259847</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.837326083791189</v>
+        <v>2.850494562459809</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.8513994809055894</v>
+        <v>0.9241159303277278</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.45394160182085</v>
+        <v>5.497571471474132</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578991</v>
+        <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.215540389087704</v>
+        <v>-5.182619192416154</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.819438750119018</v>
+        <v>2.832607228787638</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.8513994809055894</v>
+        <v>0.9241159303277278</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.416851018611202</v>
+        <v>5.460480888264485</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629879</v>
+        <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.136714731904114</v>
+        <v>-5.103793535232564</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.854901266550405</v>
+        <v>2.868069745219025</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.9302251380891798</v>
+        <v>1.002941587511318</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.468078666479307</v>
+        <v>5.511708536132589</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686402</v>
+        <v>3.868502531686404</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.94477993065024</v>
+        <v>-4.91185873397869</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.926574279658992</v>
+        <v>2.939742758327611</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.9302251380891798</v>
+        <v>1.002941587511318</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.462977759086344</v>
+        <v>5.506607628739626</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.849324044046709</v>
+        <v>3.84932404404671</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.826606552632313</v>
+        <v>-4.793685355960763</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.969197540255258</v>
+        <v>2.982366018923877</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.048398516107107</v>
+        <v>1.121114965529245</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.529235695286195</v>
+        <v>5.572865564939478</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.836463274528997</v>
+        <v>3.836463274528999</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.713191869849582</v>
+        <v>-4.680270673178032</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.043652006231377</v>
+        <v>3.056820484899997</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.161813198889838</v>
+        <v>1.234529648311977</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.626373097818861</v>
+        <v>5.670002967472143</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.805501212984012</v>
+        <v>3.805501212984013</v>
       </c>
       <c r="C2104" t="n">
         <v>4.922845401496135</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.686142832156328</v>
+        <v>-4.653221635484778</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.048031844319856</v>
+        <v>3.061200322988475</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.188862236583092</v>
+        <v>1.26157868600523</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.63616274344599</v>
+        <v>5.679792613099274</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.679388954063188</v>
+        <v>3.6825936265466</v>
       </c>
       <c r="C2105" t="n">
         <v>4.888333718867176</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.620743799895498</v>
+        <v>-4.594247216855402</v>
       </c>
       <c r="E2105" t="n">
-        <v>3.039679774595228</v>
+        <v>3.050278407811267</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.254261268843922</v>
+        <v>1.268034958382065</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.640890480173529</v>
+        <v>5.649154693896415</v>
       </c>
     </row>
   </sheetData>
